--- a/docs/테스트_체크리스트.xlsx
+++ b/docs/테스트_체크리스트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\99. 테스트\12. 기능테스트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bradkim06/study/hitec/ht_terminal/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1F1D5C-A862-4347-B0F9-8218E9139098}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7A6813-1D8A-3749-96EB-0A66AE545764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8976" xr2:uid="{7A230418-A3ED-42FF-9FF0-7BE542EF8DC3}"/>
+    <workbookView xWindow="28800" yWindow="500" windowWidth="19200" windowHeight="21100" activeTab="1" xr2:uid="{7A230418-A3ED-42FF-9FF0-7BE542EF8DC3}"/>
   </bookViews>
   <sheets>
     <sheet name="요약" sheetId="11" r:id="rId1"/>
@@ -24,19 +24,26 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">요약!$D$7:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">참고사항!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테스트 결과'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테스트 결과'!$A$1:$D$50</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="151">
   <si>
     <t>참고사항</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -166,14 +173,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Slave 상태 확인 요청이 정상적으로 동작하는지?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slave 상태 확인 동작 시도 시 진행 및 완료 여부를 확인할 수 있는지?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>주기 검침 데이터 요청이 정상적으로 동작하는지?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -225,18 +224,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>즉시 검침 동작 시도 시 다른 Slave access 동작을 인지하고 Busy를 보고하는지?</t>
-  </si>
-  <si>
     <t>즉시 검침 동작 시도 시 무선통신 동작을 인지하고 Busy를 보고하는지?</t>
   </si>
   <si>
-    <t>Slave 상태 확인 동작 시도 시 다른 Slave access 동작을 인지하고 Busy를 보고하는지?</t>
-  </si>
-  <si>
-    <t>Slave 상태 확인 동작 시도 시 MODEM 동작을 인지하고 Busy를 보고하는지?</t>
-  </si>
-  <si>
     <t>주기 검침 데이터 요청 재시도가 정상적으로 동작하는지?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -246,14 +236,6 @@
   </si>
   <si>
     <t>즉각 검침 데이터 요청 재시도가 정상적으로 동작하는지?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slave 상태정보 데이터 요청이 정상적으로 동작하는지?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slave 상태정보 데이터 요청 재시도가 정상적으로 동작하는지?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -371,21 +353,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Slave 정보
-(E)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>검침
 (A)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Slave 정보
-(B)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시간동기화
 (C)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -396,16 +368,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>저온
-(A)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고온
-(B)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Sleep/Idle
 (A)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -426,11 +388,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>온도테스트
-(F)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>소모전류
 (G)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -527,26 +484,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C-D-4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C-E-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C-E-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C-E-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C-E-4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>D-A-1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -575,14 +512,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>D-B-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D-B-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>D-C-1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -623,22 +552,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>F-A-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-A-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-B-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-B-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>G-A-1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -655,10 +568,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>G-B-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>테스트 로그</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -667,14 +576,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>고온 온도테스트 서버 로그</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>저온 온도테스트 서버 로그</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>IDLE 소모전류</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -731,49 +632,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>저온(-10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)에서 단말기가 정상적으로 동작하는지? (리셋여부, 오동작 여부 확인)
-분단위(보고주기 6분, 검침주기 2분)로 설정하여 2~3시간 테스트.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>저온(-10℃)에서 단말기 통신 상태가 원활한지?
-분단위(보고주기 6분, 검침주기 2분)로 설정하여 2~3시간 테스트.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고온(70℃)에서 단말기가 정상적으로 동작하는지? (리셋여부, 오동작 여부 확인)
-분단위(보고주기 6분, 검침주기 2분)로 설정하여 2~3시간 테스트.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고온(70℃)에서 단말기 통신 상태가 원활한지?
-분단위(보고주기 6분, 검침주기 2분)로 설정하여 2~3시간 테스트.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Active 소모전류 계산 (무선통신 100% 성공)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -782,16 +640,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Active 소모전류 계산 (무선통신 75% 성공)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Active 소모전류 계산</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>장비 확인 및 소모전류테스트 로그 참조.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -801,7 +658,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -859,13 +716,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF0070C0"/>
@@ -895,6 +745,15 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -1032,7 +891,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1096,34 +955,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1132,6 +991,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1153,8 +1015,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1369,13 +1231,9 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="요약"/>
-      <sheetName val="테스트 결과"/>
-      <sheetName val="참고사항"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1678,37 +1536,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE435518-D0A5-4124-BD73-EAE5B204DBD4}">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="34.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.69921875" customWidth="1"/>
-    <col min="5" max="5" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" customWidth="1"/>
-    <col min="7" max="8" width="8.69921875" customWidth="1"/>
+    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="8" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="18" thickBot="1">
       <c r="A1" s="13" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1" thickTop="1">
       <c r="A2" s="20"/>
       <c r="B2" s="20" t="s">
         <v>1</v>
@@ -1716,16 +1574,16 @@
       <c r="D2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-    </row>
-    <row r="3" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+    </row>
+    <row r="3" spans="1:10" ht="17.5" customHeight="1">
       <c r="A3" s="15"/>
       <c r="B3" s="15" t="s">
         <v>2</v>
@@ -1733,16 +1591,16 @@
       <c r="D3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+    </row>
+    <row r="4" spans="1:10" ht="26.5" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
         <v>4</v>
@@ -1750,16 +1608,16 @@
       <c r="D4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-    </row>
-    <row r="5" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E4" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+    </row>
+    <row r="5" spans="1:10" ht="17.5" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15" t="s">
         <v>3</v>
@@ -1767,57 +1625,59 @@
       <c r="D5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="15"/>
+      <c r="E5" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="33" t="s">
+        <v>149</v>
+      </c>
       <c r="B6" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="15"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="33" t="s">
+        <v>149</v>
+      </c>
       <c r="B7" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="40" t="s">
-        <v>180</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
+        <v>148</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="26" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="I8" s="28" t="s">
         <v>12</v>
@@ -1826,13 +1686,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>158</v>
-      </c>
+    <row r="9" spans="1:10">
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
       <c r="D9" s="17" t="str">
         <f>'테스트 결과'!A2</f>
         <v>주기동작
@@ -1843,12 +1699,12 @@
         <v>6</v>
       </c>
       <c r="F9" s="17">
-        <f t="shared" ref="F9:F15" si="0">G9+H9+I9+J9</f>
-        <v>0</v>
+        <f t="shared" ref="F9:F14" si="0">G9+H9+I9+J9</f>
+        <v>6</v>
       </c>
       <c r="G9" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, H8)</f>
@@ -1863,11 +1719,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15" t="s">
-        <v>179</v>
-      </c>
+    <row r="10" spans="1:10">
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="25"/>
       <c r="D10" s="17" t="str">
         <f>'테스트 결과'!A8</f>
@@ -1880,11 +1734,11 @@
       </c>
       <c r="F10" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H10" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, H8)</f>
@@ -1899,7 +1753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10">
       <c r="A11" s="32"/>
       <c r="B11" s="32"/>
       <c r="D11" s="17" t="str">
@@ -1909,15 +1763,15 @@
       </c>
       <c r="E11" s="17">
         <f>COUNTIF('테스트 결과'!C:C,"C-*")</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H11" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, H8)</f>
@@ -1932,25 +1786,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10">
       <c r="A12" s="32"/>
       <c r="B12" s="32"/>
       <c r="D12" s="17" t="str">
-        <f>'테스트 결과'!A34</f>
+        <f>'테스트 결과'!A29</f>
         <v>RF424/433
 (D)</v>
       </c>
       <c r="E12" s="17">
         <f>COUNTIF('테스트 결과'!C:C,"D-*")</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G12" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H12" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, H8)</f>
@@ -1965,11 +1819,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
+    <row r="13" spans="1:10" ht="18" customHeight="1">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="D13" s="17" t="str">
-        <f>'테스트 결과'!A48</f>
+        <f>'테스트 결과'!A41</f>
         <v>계량기 통신
 (E)</v>
       </c>
@@ -1979,11 +1833,11 @@
       </c>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, H8)</f>
@@ -1998,110 +1852,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
+    <row r="14" spans="1:10" ht="17.5" customHeight="1">
       <c r="D14" s="17" t="str">
-        <f>'테스트 결과'!A53</f>
-        <v>온도테스트
-(F)</v>
+        <f>'테스트 결과'!A46</f>
+        <v>소모전류
+(G)</v>
       </c>
       <c r="E14" s="17">
-        <f>COUNTIF('테스트 결과'!C:C,"F-*")</f>
-        <v>4</v>
+        <f>COUNTIF('테스트 결과'!C:C,"G-*")</f>
+        <v>5</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "F-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "F-*", '테스트 결과'!D:D, H8)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "F-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "F-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="D15" s="17" t="str">
-        <f>'테스트 결과'!A57</f>
-        <v>소모전류
-(G)</v>
-      </c>
-      <c r="E15" s="17">
-        <f>COUNTIF('테스트 결과'!C:C,"G-*")</f>
-        <v>6</v>
-      </c>
-      <c r="F15" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, G8)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H14" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I14" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, I8)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J14" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, J8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="D16" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="E16" s="17">
-        <f>E9+E10+E11+E12+E13+E14+E15</f>
-        <v>61</v>
-      </c>
-      <c r="F16" s="17">
-        <f>F9+F10+F11+F12+F13+F14+F15</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="17">
-        <f t="shared" ref="G16:J16" si="1">G9+G10+G11+G12+G13+G14+G15</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="17">
+    <row r="15" spans="1:10" ht="17.5" customHeight="1">
+      <c r="D15" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="17">
+        <f>E9+E10+E11+E12+E13+E14</f>
+        <v>49</v>
+      </c>
+      <c r="F15" s="17">
+        <f t="shared" ref="F15:J15" si="1">F9+F10+F11+F12+F13+F14</f>
+        <v>44</v>
+      </c>
+      <c r="G15" s="17">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="H15" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I15" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J15" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
+    <row r="19" spans="1:2">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2142,18 +1959,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
       <formula>$E$14</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
-      <formula>$E$15</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="notEqual">
-      <formula>$E$16</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2166,22 +1973,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10.69921875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="2" width="10.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="60.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="16" thickBot="1">
       <c r="A1" s="13" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>17</v>
@@ -2193,759 +2000,700 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.2" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>69</v>
+    <row r="2" spans="1:5" ht="16" thickTop="1">
+      <c r="A2" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>62</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="7"/>
+        <v>83</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>150</v>
+      </c>
       <c r="E2" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E3" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="9"/>
+        <v>85</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38" t="s">
-        <v>70</v>
+    <row r="5" spans="1:5">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39" t="s">
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="9"/>
+        <v>87</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E7" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="8" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="30">
+      <c r="A14" s="39"/>
+      <c r="B14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30">
+      <c r="A15" s="39"/>
+      <c r="B15" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="8" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A14" s="38"/>
-      <c r="B14" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A15" s="38"/>
-      <c r="B15" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>77</v>
+    <row r="19" spans="1:5">
+      <c r="A19" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>70</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="9"/>
+        <v>82</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E19" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
+    <row r="20" spans="1:5">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="9"/>
+        <v>100</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E20" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
+    <row r="21" spans="1:5">
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E21" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A22" s="38"/>
+    <row r="22" spans="1:5" ht="30">
+      <c r="A22" s="39"/>
       <c r="B22" s="10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E22" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38" t="s">
-        <v>79</v>
+    <row r="23" spans="1:5">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39" t="s">
+        <v>72</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="9"/>
+        <v>103</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E23" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
+    <row r="24" spans="1:5">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E24" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A25" s="38"/>
-      <c r="B25" s="38"/>
+    <row r="25" spans="1:5">
+      <c r="A25" s="39"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="9"/>
+        <v>105</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E25" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A26" s="38"/>
-      <c r="B26" s="38" t="s">
-        <v>80</v>
+    <row r="26" spans="1:5">
+      <c r="A26" s="39"/>
+      <c r="B26" s="39" t="s">
+        <v>73</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" s="9"/>
+        <v>106</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E26" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A27" s="38"/>
-      <c r="B27" s="38"/>
+    <row r="27" spans="1:5" ht="30">
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="39"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="30">
+      <c r="A35" s="39"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="39"/>
+      <c r="B36" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="39"/>
+      <c r="B38" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="39"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="5" t="s">
+      <c r="D39" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="39"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A29" s="38"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="5" t="s">
+      <c r="D40" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30" s="38"/>
-      <c r="B30" s="38" t="s">
+      <c r="D41" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="39"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="39"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="30">
+      <c r="A45" s="39"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A31" s="38"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="38"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="18" t="s">
+      <c r="B46" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="38"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="18" t="s">
+      <c r="D46" s="41"/>
+      <c r="E46" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="39"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="18" t="s">
+      <c r="D47" s="41"/>
+      <c r="E47" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="39"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="41"/>
+      <c r="E48" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="39"/>
+      <c r="B49" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="38"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="18" t="s">
+      <c r="D49" s="41"/>
+      <c r="E49" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="38"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="38"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A40" s="38"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A41" s="38"/>
-      <c r="B41" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A42" s="38"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A43" s="38"/>
-      <c r="B43" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A44" s="38"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A45" s="38"/>
-      <c r="B45" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A46" s="38"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A47" s="38"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A48" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="B48" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A49" s="38"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A50" s="38"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A51" s="38"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A52" s="38"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A53" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A54" s="38"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D54" s="9"/>
-      <c r="E54" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A55" s="38"/>
-      <c r="B55" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="D50" s="41"/>
+      <c r="E50" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
-      <c r="A56" s="38"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A57" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="B57" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A58" s="38"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D58" s="9"/>
-      <c r="E58" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A59" s="38"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D59" s="9"/>
-      <c r="E59" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A60" s="38"/>
-      <c r="B60" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D60" s="9"/>
-      <c r="E60" s="31" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A61" s="38"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D61" s="9"/>
-      <c r="E61" s="31" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A62" s="38"/>
-      <c r="B62" s="38"/>
-      <c r="C62" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D62" s="9"/>
-      <c r="E62" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    </row>
+    <row r="56" spans="1:5" ht="18" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:D62" xr:uid="{CA9F09DA-C197-4104-89A1-F7CCEE08673B}"/>
-  <mergeCells count="24">
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B48:B52"/>
+  <autoFilter ref="A1:D50" xr:uid="{CA9F09DA-C197-4104-89A1-F7CCEE08673B}"/>
+  <mergeCells count="19">
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="A8:A18"/>
+    <mergeCell ref="A19:A28"/>
+    <mergeCell ref="A29:A40"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="A41:A45"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B13"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B34:B40"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B29:B35"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B19:B21"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="A8:A18"/>
-    <mergeCell ref="A19:A33"/>
-    <mergeCell ref="A34:A47"/>
-    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B41:B45"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.6" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2998,70 +2746,17 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>D76:D1048576 D2:D59 D63</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{5726B4D1-365F-43EA-A6FF-3AE0429B08E4}">
-            <xm:f>'C:\_SoftwareOK\Q-Dir\2018-11-22 (NB-IoT)\[HAT-435W_U103_테스트_체크리스트.xlsx]요약'!#REF!</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color theme="1"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{82D6426B-931C-4192-B8D7-DD647F185995}">
-            <xm:f>'C:\_SoftwareOK\Q-Dir\2018-11-22 (NB-IoT)\[HAT-435W_U103_테스트_체크리스트.xlsx]요약'!#REF!</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color theme="0" tint="-0.499984740745262"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{A058FCB5-7AC2-452A-9EDA-48516B359337}">
-            <xm:f>'C:\_SoftwareOK\Q-Dir\2018-11-22 (NB-IoT)\[HAT-435W_U103_테스트_체크리스트.xlsx]요약'!#REF!</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{F3F44DDA-9D76-412E-AC96-91EF107E0A93}">
-            <xm:f>'C:\_SoftwareOK\Q-Dir\2018-11-22 (NB-IoT)\[HAT-435W_U103_테스트_체크리스트.xlsx]요약'!#REF!</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color rgb="FF0070C0"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>D60:D62</xm:sqref>
+          <xm:sqref>D64:D1048576 D51 D2:D18</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4C8205F-1336-4B23-BA34-568AD180CEF1}">
           <x14:formula1>
             <xm:f>요약!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D59</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7871C9AA-8836-4671-9901-0514A2D6079B}">
-          <x14:formula1>
-            <xm:f>'[HAT-435W_U103_테스트_체크리스트.xlsx]요약'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>D60:D62</xm:sqref>
+          <xm:sqref>D2:D18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3075,56 +2770,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.69921875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="10.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="16" thickBot="1">
       <c r="A1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.2" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="16" thickTop="1">
       <c r="A2" s="5"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="15">
       <c r="A3" s="5"/>
       <c r="B3" s="9"/>
       <c r="C3" s="8"/>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="15">
       <c r="A4" s="5"/>
       <c r="B4" s="9"/>
       <c r="C4" s="8"/>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="15">
       <c r="A5" s="5"/>
       <c r="B5" s="9"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" s="5"/>
       <c r="B6" s="9"/>
       <c r="C6" s="8"/>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" s="18"/>
       <c r="B7" s="9"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="15">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
       <c r="C8" s="11"/>

--- a/docs/테스트_체크리스트.xlsx
+++ b/docs/테스트_체크리스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bradkim06/study/hitec/ht_terminal/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7A6813-1D8A-3749-96EB-0A66AE545764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D66533-22FF-6A4D-909B-1D735C42AD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="500" windowWidth="19200" windowHeight="21100" activeTab="1" xr2:uid="{7A230418-A3ED-42FF-9FF0-7BE542EF8DC3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="151">
   <si>
     <t>참고사항</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1864,11 +1864,11 @@
       </c>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, G8)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14" s="17">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, H8)</f>
@@ -1893,11 +1893,11 @@
       </c>
       <c r="F15" s="17">
         <f t="shared" ref="F15:J15" si="1">F9+F10+F11+F12+F13+F14</f>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" si="1"/>
@@ -2620,7 +2620,9 @@
       <c r="C46" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D46" s="41"/>
+      <c r="D46" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E46" s="8" t="s">
         <v>16</v>
       </c>
@@ -2631,7 +2633,9 @@
       <c r="C47" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D47" s="41"/>
+      <c r="D47" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E47" s="8" t="s">
         <v>135</v>
       </c>
@@ -2642,7 +2646,9 @@
       <c r="C48" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D48" s="41"/>
+      <c r="D48" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E48" s="8" t="s">
         <v>136</v>
       </c>
@@ -2655,7 +2661,9 @@
       <c r="C49" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D49" s="41"/>
+      <c r="D49" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E49" s="31" t="s">
         <v>146</v>
       </c>
@@ -2666,7 +2674,9 @@
       <c r="C50" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D50" s="41"/>
+      <c r="D50" s="41" t="s">
+        <v>150</v>
+      </c>
       <c r="E50" s="31" t="s">
         <v>147</v>
       </c>

--- a/docs/테스트_체크리스트.xlsx
+++ b/docs/테스트_체크리스트.xlsx
@@ -8,22 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bradkim06/study/hitec/ht_terminal/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D66533-22FF-6A4D-909B-1D735C42AD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B28AA06-6B5E-C24D-B1FF-56D17868AD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="500" windowWidth="19200" windowHeight="21100" activeTab="1" xr2:uid="{7A230418-A3ED-42FF-9FF0-7BE542EF8DC3}"/>
+    <workbookView xWindow="28800" yWindow="500" windowWidth="19200" windowHeight="21100" xr2:uid="{7A230418-A3ED-42FF-9FF0-7BE542EF8DC3}"/>
   </bookViews>
   <sheets>
     <sheet name="요약" sheetId="11" r:id="rId1"/>
     <sheet name="테스트 결과" sheetId="1" r:id="rId2"/>
-    <sheet name="참고사항" sheetId="17" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">요약!$D$7:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">참고사항!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">요약!$B$7:$H$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테스트 결과'!$A$1:$D$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,8 +28,11 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,27 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="151">
-  <si>
-    <t>참고사항</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간단위 정상 동작 로그</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>분단위 정상 동작 로그</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slave 및 무선통신 실패 로그 (3분단위 통신 동작, 1시간)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>초기 Slave 통신이 동작 도중 복구되는 경우의 로그 (3분단위 통신 동작, 20분)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="140">
   <si>
     <t xml:space="preserve">검침 데이터를 못읽어 올 경우 MT_DOWN으로 저장하는지? </t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -568,22 +545,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>테스트 로그</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>테스트 결과 종류</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>IDLE 소모전류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sleep 소모전류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>G-A-3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -596,22 +561,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Fail</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pass</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>결과</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Fail</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pass</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>총 개수</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -637,14 +598,6 @@
   </si>
   <si>
     <t>Active 소모전류 계산 (무선통신 0% 성공)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Active 소모전류 계산</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 확인 및 소모전류테스트 로그 참조.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -760,7 +713,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,12 +728,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -891,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -901,9 +848,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -925,9 +869,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -938,12 +879,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -952,9 +887,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -988,11 +920,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1013,9 +942,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1023,71 +949,7 @@
     <cellStyle name="보통" xfId="1" builtinId="28"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <b/>
@@ -1180,26 +1042,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1211,32 +1053,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="요약"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="요약"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1536,431 +1352,371 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE435518-D0A5-4124-BD73-EAE5B204DBD4}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="8" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" thickBot="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" ht="18" thickBot="1">
+      <c r="B1" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" thickTop="1">
+      <c r="B2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="17.5" customHeight="1">
+      <c r="B3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+    </row>
+    <row r="4" spans="1:8" ht="26.5" customHeight="1">
+      <c r="B4" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+    </row>
+    <row r="5" spans="1:8" ht="17.5" customHeight="1">
+      <c r="B5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1" thickTop="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-    </row>
-    <row r="3" spans="1:10" ht="17.5" customHeight="1">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15" t="s">
+      <c r="F8" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-    </row>
-    <row r="4" spans="1:10" ht="26.5" customHeight="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-    </row>
-    <row r="5" spans="1:10" ht="17.5" customHeight="1">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="D9" s="17" t="str">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="13" t="str">
         <f>'테스트 결과'!A2</f>
         <v>주기동작
 (A)</v>
       </c>
-      <c r="E9" s="17">
+      <c r="C9" s="13">
         <f>COUNTIF('테스트 결과'!C:C,"A-*")</f>
         <v>6</v>
       </c>
-      <c r="F9" s="17">
-        <f t="shared" ref="F9:F14" si="0">G9+H9+I9+J9</f>
+      <c r="D9" s="13">
+        <f t="shared" ref="D9:D14" si="0">E9+F9+G9+H9</f>
         <v>6</v>
       </c>
-      <c r="G9" s="17">
+      <c r="E9" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, E8)</f>
+        <v>6</v>
+      </c>
+      <c r="F9" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, G8)</f>
-        <v>6</v>
-      </c>
-      <c r="H9" s="17">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "A-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="17" t="str">
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="20"/>
+      <c r="B10" s="13" t="str">
         <f>'테스트 결과'!A8</f>
         <v>무선통신
 (B)</v>
       </c>
-      <c r="E10" s="17">
+      <c r="C10" s="13">
         <f>COUNTIF('테스트 결과'!C:C,"B-*")</f>
         <v>11</v>
       </c>
-      <c r="F10" s="17">
+      <c r="D10" s="13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G10" s="17">
+      <c r="E10" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, E8)</f>
+        <v>11</v>
+      </c>
+      <c r="F10" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, G8)</f>
-        <v>11</v>
-      </c>
-      <c r="H10" s="17">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "B-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
-      <c r="D11" s="17" t="str">
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="13" t="str">
         <f>'테스트 결과'!A19</f>
         <v>NFC 동작
 (C)</v>
       </c>
-      <c r="E11" s="17">
+      <c r="C11" s="13">
         <f>COUNTIF('테스트 결과'!C:C,"C-*")</f>
         <v>10</v>
       </c>
-      <c r="F11" s="17">
+      <c r="D11" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G11" s="17">
+      <c r="E11" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, E8)</f>
+        <v>10</v>
+      </c>
+      <c r="F11" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, G8)</f>
-        <v>10</v>
-      </c>
-      <c r="H11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "C-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="D12" s="17" t="str">
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="13" t="str">
         <f>'테스트 결과'!A29</f>
         <v>RF424/433
 (D)</v>
       </c>
-      <c r="E12" s="17">
+      <c r="C12" s="13">
         <f>COUNTIF('테스트 결과'!C:C,"D-*")</f>
         <v>12</v>
       </c>
-      <c r="F12" s="17">
+      <c r="D12" s="13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G12" s="17">
+      <c r="E12" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, E8)</f>
+        <v>12</v>
+      </c>
+      <c r="F12" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, G8)</f>
-        <v>12</v>
-      </c>
-      <c r="H12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "D-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="18" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="D13" s="17" t="str">
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="B13" s="13" t="str">
         <f>'테스트 결과'!A41</f>
         <v>계량기 통신
 (E)</v>
       </c>
-      <c r="E13" s="17">
+      <c r="C13" s="13">
         <f>COUNTIF('테스트 결과'!C:C,"E-*")</f>
         <v>5</v>
       </c>
-      <c r="F13" s="17">
+      <c r="D13" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G13" s="17">
+      <c r="E13" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, E8)</f>
+        <v>5</v>
+      </c>
+      <c r="F13" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, G8)</f>
-        <v>5</v>
-      </c>
-      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "E-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="17.5" customHeight="1">
-      <c r="D14" s="17" t="str">
+    </row>
+    <row r="14" spans="1:8" ht="17.5" customHeight="1">
+      <c r="B14" s="13" t="str">
         <f>'테스트 결과'!A46</f>
         <v>소모전류
 (G)</v>
       </c>
-      <c r="E14" s="17">
+      <c r="C14" s="13">
         <f>COUNTIF('테스트 결과'!C:C,"G-*")</f>
         <v>5</v>
       </c>
-      <c r="F14" s="17">
+      <c r="D14" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G14" s="17">
+      <c r="E14" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, E8)</f>
+        <v>5</v>
+      </c>
+      <c r="F14" s="13">
+        <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, G8)</f>
-        <v>5</v>
-      </c>
-      <c r="H14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
         <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, H8)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="17">
-        <f>COUNTIFS('테스트 결과'!C:C, "G-*", '테스트 결과'!D:D, J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="17.5" customHeight="1">
-      <c r="D15" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="17">
-        <f>E9+E10+E11+E12+E13+E14</f>
+    </row>
+    <row r="15" spans="1:8" ht="17.5" customHeight="1">
+      <c r="B15" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="13">
+        <f>C9+C10+C11+C12+C13+C14</f>
         <v>49</v>
       </c>
-      <c r="F15" s="17">
-        <f t="shared" ref="F15:J15" si="1">F9+F10+F11+F12+F13+F14</f>
+      <c r="D15" s="13">
+        <f t="shared" ref="D15:H15" si="1">D9+D10+D11+D12+D13+D14</f>
         <v>49</v>
       </c>
-      <c r="G15" s="17">
+      <c r="E15" s="13">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="H15" s="17">
+      <c r="F15" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="17">
+      <c r="G15" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="17">
+      <c r="H15" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:H7"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="notEqual">
-      <formula>$E$9</formula>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="cellIs" dxfId="9" priority="14" operator="notEqual">
+      <formula>$C$9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="cellIs" dxfId="18" priority="12" operator="notEqual">
-      <formula>$E$10</formula>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="notEqual">
+      <formula>$C$10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="notEqual">
-      <formula>$E$11</formula>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="notEqual">
+      <formula>$C$11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="notEqual">
-      <formula>$E$12</formula>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="notEqual">
+      <formula>$C$12</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="notEqual">
-      <formula>$E$13</formula>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
+      <formula>$C$13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
-      <formula>$E$14</formula>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="notEqual">
+      <formula>$C$14</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1977,720 +1733,717 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="60.6640625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16" thickBot="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16" thickTop="1">
+      <c r="A2" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B8" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30">
+      <c r="A14" s="33"/>
+      <c r="B14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30">
+      <c r="A15" s="33"/>
+      <c r="B15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="33"/>
+      <c r="B16" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30">
+      <c r="A22" s="33"/>
+      <c r="B22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="33"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="33"/>
+      <c r="B26" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="30">
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="33"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="33"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="30">
+      <c r="A35" s="33"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="33"/>
+      <c r="B36" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="33"/>
+      <c r="B38" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="33"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="33"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="13" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="33"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" thickTop="1">
-      <c r="A2" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="33"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="33"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="30">
+      <c r="A45" s="33"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30">
-      <c r="A14" s="39"/>
-      <c r="B14" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30">
-      <c r="A15" s="39"/>
-      <c r="B15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="39"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="39"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30">
-      <c r="A22" s="39"/>
-      <c r="B22" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="39"/>
-      <c r="B23" s="39" t="s">
+    <row r="46" spans="1:5">
+      <c r="A46" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="39"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="39"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="39"/>
-      <c r="B26" s="39" t="s">
+      <c r="C46" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="33"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="33"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="33"/>
+      <c r="B49" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30">
-      <c r="A27" s="39"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="39"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="39"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="39"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D31" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="39"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="39"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="30">
-      <c r="A35" s="39"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="39"/>
-      <c r="B36" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="39"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="39"/>
-      <c r="B38" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="39"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="39"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="39"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="39"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="39"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="5" t="s">
+      <c r="D49" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="33"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="30">
-      <c r="A45" s="39"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D45" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="39"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="39"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D48" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="39"/>
-      <c r="B49" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D49" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E49" s="31" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="39"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" s="31" t="s">
-        <v>147</v>
+      <c r="D50" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:D50" xr:uid="{CA9F09DA-C197-4104-89A1-F7CCEE08673B}"/>
   <mergeCells count="19">
-    <mergeCell ref="A46:A50"/>
-    <mergeCell ref="A8:A18"/>
-    <mergeCell ref="A19:A28"/>
-    <mergeCell ref="A29:A40"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B41:B45"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B13"/>
@@ -2701,9 +2454,12 @@
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B41:B45"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="A8:A18"/>
+    <mergeCell ref="A19:A28"/>
+    <mergeCell ref="A29:A40"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A41:A45"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.6" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2713,7 +2469,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="137" operator="equal" id="{C1021C36-1F34-4E96-AEEF-266101762287}">
-            <xm:f>요약!$D$5</xm:f>
+            <xm:f>요약!$B$5</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -2724,7 +2480,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="138" operator="equal" id="{E17C41FA-0399-49AD-A7D8-41D51974F3FE}">
-            <xm:f>요약!$D$4</xm:f>
+            <xm:f>요약!$B$4</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -2735,7 +2491,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="139" operator="equal" id="{EAF21A1C-E852-42CF-8584-27E6BC41F875}">
-            <xm:f>요약!$D$3</xm:f>
+            <xm:f>요약!$B$3</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -2746,7 +2502,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="140" operator="equal" id="{9E8A2780-B292-407D-B8C8-0550A5393312}">
-            <xm:f>요약!$D$2</xm:f>
+            <xm:f>요약!$B$2</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -2764,7 +2520,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4C8205F-1336-4B23-BA34-568AD180CEF1}">
           <x14:formula1>
-            <xm:f>요약!$D$2:$D$5</xm:f>
+            <xm:f>요약!$B$2:$B$5</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D18</xm:sqref>
         </x14:dataValidation>
@@ -2772,125 +2528,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445C94CC-22FA-44FD-9406-DEC80EB11DC2}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="10.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="45.6640625" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="8.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16" thickBot="1">
-      <c r="A1" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16" thickTop="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="5"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="5"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="8"/>
-    </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="A7" s="18"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" ht="15">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="11"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{C79A2A87-01F9-4E20-B210-7CF0A1186459}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="141" operator="equal" id="{AC9E8AE3-C4F5-43FA-ABC0-FF144DF9242E}">
-            <xm:f>요약!$D$5</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color theme="1"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="142" operator="equal" id="{38BEB4B1-E17C-4C64-B8BC-3D89D2CF13DC}">
-            <xm:f>요약!$D$4</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color theme="0" tint="-0.499984740745262"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="143" operator="equal" id="{51507EA4-C557-4AC3-8E4C-ABA467C026BC}">
-            <xm:f>요약!$D$3</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="144" operator="equal" id="{B2250996-E9C3-4981-89D0-D7BE4856F135}">
-            <xm:f>요약!$D$2</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <strike val="0"/>
-                <color rgb="FF0070C0"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B76:B1048576 B2:B63</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
 </file>